--- a/gu_in/Map.edf/Elan.xlsx
+++ b/gu_in/Map.edf/Elan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project RF X\Parser_Public_Releases\Parser_1.0.2\database\gu_in\Map.edf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\emay.dev\Parser_1.0.2\Database\gu_in\Map.edf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C861A334-004E-4601-A142-9BB994FD789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7555C74A-AD88-44F2-8712-C3D6CF5F83B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14235" yWindow="690" windowWidth="10110" windowHeight="11205" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1600,13 +1598,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1616,6 +1614,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1638,9 +1642,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1976,9 +1981,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1989,7 +1994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2000,7 +2005,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2011,7 +2016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2022,7 +2027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2033,7 +2038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2044,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2055,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2066,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -2077,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -2088,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -2099,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -2110,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -2121,7 +2126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -2132,7 +2137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -2143,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -2154,7 +2159,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -2165,7 +2170,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -2176,7 +2181,7 @@
         <v>-516</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -2187,7 +2192,7 @@
         <v>-577</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -2198,7 +2203,7 @@
         <v>15199</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -2209,7 +2214,7 @@
         <v>15198</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
@@ -2220,7 +2225,7 @@
         <v>249891</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -2231,7 +2236,7 @@
         <v>201730</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -2250,9 +2255,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2338,7 +2343,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28">
       <c r="A2" s="1" t="s">
         <v>37</v>
       </c>
@@ -2424,7 +2429,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -2510,7 +2515,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
         <v>67</v>
       </c>
@@ -2596,7 +2601,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
@@ -2682,7 +2687,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -2768,7 +2773,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28">
       <c r="A7" s="1" t="s">
         <v>76</v>
       </c>
@@ -2854,7 +2859,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -2948,9 +2953,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2976,7 +2981,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
@@ -3010,9 +3015,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -3029,7 +3034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -3046,7 +3051,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
         <v>137</v>
       </c>
@@ -3063,7 +3068,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
         <v>123</v>
       </c>
@@ -3080,7 +3085,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>148</v>
       </c>
@@ -3097,7 +3102,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>288</v>
       </c>
@@ -3122,9 +3127,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J311"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -3156,7 +3161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -3188,7 +3193,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>100</v>
       </c>
@@ -3202,7 +3207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>100</v>
       </c>
@@ -3234,7 +3239,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>103</v>
       </c>
@@ -3248,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
         <v>103</v>
       </c>
@@ -3280,7 +3285,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
         <v>106</v>
       </c>
@@ -3294,7 +3299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
         <v>106</v>
       </c>
@@ -3326,7 +3331,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
         <v>109</v>
       </c>
@@ -3340,7 +3345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
         <v>109</v>
       </c>
@@ -3372,7 +3377,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
         <v>112</v>
       </c>
@@ -3386,7 +3391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
         <v>112</v>
       </c>
@@ -3418,7 +3423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
         <v>115</v>
       </c>
@@ -3432,7 +3437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
         <v>115</v>
       </c>
@@ -3464,7 +3469,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
         <v>117</v>
       </c>
@@ -3478,7 +3483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
         <v>117</v>
       </c>
@@ -3510,7 +3515,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
         <v>122</v>
       </c>
@@ -3524,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>122</v>
       </c>
@@ -3556,7 +3561,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
         <v>128</v>
       </c>
@@ -3570,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
         <v>128</v>
       </c>
@@ -3602,7 +3607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>132</v>
       </c>
@@ -3616,7 +3621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>132</v>
       </c>
@@ -3648,7 +3653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
         <v>135</v>
       </c>
@@ -3662,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
         <v>135</v>
       </c>
@@ -3694,7 +3699,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
         <v>135</v>
       </c>
@@ -3726,7 +3731,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
         <v>135</v>
       </c>
@@ -3758,7 +3763,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
         <v>135</v>
       </c>
@@ -3790,7 +3795,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
         <v>141</v>
       </c>
@@ -3804,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
         <v>141</v>
       </c>
@@ -3836,7 +3841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -3868,7 +3873,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
         <v>141</v>
       </c>
@@ -3900,7 +3905,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
         <v>141</v>
       </c>
@@ -3932,7 +3937,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
         <v>148</v>
       </c>
@@ -3946,7 +3951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
         <v>148</v>
       </c>
@@ -3978,7 +3983,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
         <v>148</v>
       </c>
@@ -4010,7 +4015,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
         <v>148</v>
       </c>
@@ -4042,7 +4047,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
         <v>148</v>
       </c>
@@ -4074,7 +4079,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
         <v>154</v>
       </c>
@@ -4088,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
         <v>154</v>
       </c>
@@ -4120,7 +4125,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
         <v>154</v>
       </c>
@@ -4152,7 +4157,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
         <v>154</v>
       </c>
@@ -4184,7 +4189,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
         <v>154</v>
       </c>
@@ -4216,7 +4221,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
         <v>162</v>
       </c>
@@ -4230,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>162</v>
       </c>
@@ -4262,7 +4267,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
         <v>162</v>
       </c>
@@ -4294,7 +4299,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
         <v>162</v>
       </c>
@@ -4326,7 +4331,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
         <v>162</v>
       </c>
@@ -4358,7 +4363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
         <v>170</v>
       </c>
@@ -4372,7 +4377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
         <v>170</v>
       </c>
@@ -4404,7 +4409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
         <v>170</v>
       </c>
@@ -4436,7 +4441,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
         <v>177</v>
       </c>
@@ -4450,7 +4455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
         <v>177</v>
       </c>
@@ -4482,7 +4487,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
         <v>177</v>
       </c>
@@ -4514,7 +4519,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="1" t="s">
         <v>177</v>
       </c>
@@ -4546,7 +4551,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10">
       <c r="A55" s="1" t="s">
         <v>177</v>
       </c>
@@ -4578,7 +4583,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" s="1" t="s">
         <v>177</v>
       </c>
@@ -4610,7 +4615,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" s="1" t="s">
         <v>177</v>
       </c>
@@ -4642,7 +4647,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" s="1" t="s">
         <v>177</v>
       </c>
@@ -4674,7 +4679,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" s="1" t="s">
         <v>177</v>
       </c>
@@ -4706,7 +4711,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60" s="1" t="s">
         <v>188</v>
       </c>
@@ -4720,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61" s="1" t="s">
         <v>188</v>
       </c>
@@ -4752,7 +4757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62" s="1" t="s">
         <v>188</v>
       </c>
@@ -4784,7 +4789,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10">
       <c r="A63" s="1" t="s">
         <v>188</v>
       </c>
@@ -4816,7 +4821,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10">
       <c r="A64" s="1" t="s">
         <v>188</v>
       </c>
@@ -4848,7 +4853,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10">
       <c r="A65" s="1" t="s">
         <v>193</v>
       </c>
@@ -4862,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10">
       <c r="A66" s="1" t="s">
         <v>193</v>
       </c>
@@ -4894,7 +4899,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10">
       <c r="A67" s="1" t="s">
         <v>193</v>
       </c>
@@ -4926,7 +4931,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10">
       <c r="A68" s="1" t="s">
         <v>193</v>
       </c>
@@ -4958,7 +4963,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10">
       <c r="A69" s="1" t="s">
         <v>193</v>
       </c>
@@ -4990,7 +4995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10">
       <c r="A70" s="1" t="s">
         <v>202</v>
       </c>
@@ -5004,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10">
       <c r="A71" s="1" t="s">
         <v>202</v>
       </c>
@@ -5036,7 +5041,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10">
       <c r="A72" s="1" t="s">
         <v>202</v>
       </c>
@@ -5068,7 +5073,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10">
       <c r="A73" s="1" t="s">
         <v>202</v>
       </c>
@@ -5100,7 +5105,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10">
       <c r="A74" s="1" t="s">
         <v>202</v>
       </c>
@@ -5132,7 +5137,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10">
       <c r="A75" s="1" t="s">
         <v>208</v>
       </c>
@@ -5146,7 +5151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10">
       <c r="A76" s="1" t="s">
         <v>208</v>
       </c>
@@ -5178,7 +5183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10">
       <c r="A77" s="1" t="s">
         <v>208</v>
       </c>
@@ -5210,7 +5215,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10">
       <c r="A78" s="1" t="s">
         <v>208</v>
       </c>
@@ -5242,7 +5247,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10">
       <c r="A79" s="1" t="s">
         <v>208</v>
       </c>
@@ -5274,7 +5279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10">
       <c r="A80" s="1" t="s">
         <v>214</v>
       </c>
@@ -5288,7 +5293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10">
       <c r="A81" s="1" t="s">
         <v>214</v>
       </c>
@@ -5320,7 +5325,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10">
       <c r="A82" s="1" t="s">
         <v>214</v>
       </c>
@@ -5352,7 +5357,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10">
       <c r="A83" s="1" t="s">
         <v>214</v>
       </c>
@@ -5384,7 +5389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10">
       <c r="A84" s="1" t="s">
         <v>214</v>
       </c>
@@ -5416,7 +5421,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10">
       <c r="A85" s="1" t="s">
         <v>220</v>
       </c>
@@ -5430,7 +5435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10">
       <c r="A86" s="1" t="s">
         <v>220</v>
       </c>
@@ -5462,7 +5467,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10">
       <c r="A87" s="1" t="s">
         <v>220</v>
       </c>
@@ -5494,7 +5499,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10">
       <c r="A88" s="1" t="s">
         <v>220</v>
       </c>
@@ -5526,7 +5531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10">
       <c r="A89" s="1" t="s">
         <v>220</v>
       </c>
@@ -5558,7 +5563,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10">
       <c r="A90" s="1" t="s">
         <v>225</v>
       </c>
@@ -5572,7 +5577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10">
       <c r="A91" s="1" t="s">
         <v>225</v>
       </c>
@@ -5604,7 +5609,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10">
       <c r="A92" s="1" t="s">
         <v>225</v>
       </c>
@@ -5636,7 +5641,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10">
       <c r="A93" s="1" t="s">
         <v>225</v>
       </c>
@@ -5668,7 +5673,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10">
       <c r="A94" s="1" t="s">
         <v>225</v>
       </c>
@@ -5700,7 +5705,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10">
       <c r="A95" s="1" t="s">
         <v>230</v>
       </c>
@@ -5714,7 +5719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10">
       <c r="A96" s="1" t="s">
         <v>230</v>
       </c>
@@ -5746,7 +5751,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10">
       <c r="A97" s="1" t="s">
         <v>230</v>
       </c>
@@ -5778,7 +5783,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10">
       <c r="A98" s="1" t="s">
         <v>230</v>
       </c>
@@ -5810,7 +5815,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10">
       <c r="A99" s="1" t="s">
         <v>230</v>
       </c>
@@ -5842,7 +5847,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10">
       <c r="A100" s="1" t="s">
         <v>235</v>
       </c>
@@ -5856,7 +5861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10">
       <c r="A101" s="1" t="s">
         <v>235</v>
       </c>
@@ -5888,7 +5893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10">
       <c r="A102" s="1" t="s">
         <v>235</v>
       </c>
@@ -5920,7 +5925,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10">
       <c r="A103" s="1" t="s">
         <v>235</v>
       </c>
@@ -5952,7 +5957,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10">
       <c r="A104" s="1" t="s">
         <v>235</v>
       </c>
@@ -5984,7 +5989,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10">
       <c r="A105" s="1" t="s">
         <v>243</v>
       </c>
@@ -5998,7 +6003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10">
       <c r="A106" s="1" t="s">
         <v>243</v>
       </c>
@@ -6030,7 +6035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10">
       <c r="A107" s="1" t="s">
         <v>243</v>
       </c>
@@ -6062,7 +6067,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10">
       <c r="A108" s="1" t="s">
         <v>243</v>
       </c>
@@ -6094,7 +6099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10">
       <c r="A109" s="1" t="s">
         <v>243</v>
       </c>
@@ -6126,7 +6131,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10">
       <c r="A110" s="1" t="s">
         <v>249</v>
       </c>
@@ -6140,7 +6145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10">
       <c r="A111" s="1" t="s">
         <v>249</v>
       </c>
@@ -6172,7 +6177,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10">
       <c r="A112" s="1" t="s">
         <v>251</v>
       </c>
@@ -6186,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10">
       <c r="A113" s="1" t="s">
         <v>251</v>
       </c>
@@ -6218,7 +6223,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10">
       <c r="A114" s="1" t="s">
         <v>251</v>
       </c>
@@ -6250,7 +6255,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10">
       <c r="A115" s="1" t="s">
         <v>251</v>
       </c>
@@ -6282,7 +6287,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10">
       <c r="A116" s="1" t="s">
         <v>251</v>
       </c>
@@ -6314,7 +6319,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10">
       <c r="A117" s="1" t="s">
         <v>257</v>
       </c>
@@ -6328,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10">
       <c r="A118" s="1" t="s">
         <v>257</v>
       </c>
@@ -6360,7 +6365,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10">
       <c r="A119" s="1" t="s">
         <v>257</v>
       </c>
@@ -6392,7 +6397,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10">
       <c r="A120" s="1" t="s">
         <v>257</v>
       </c>
@@ -6424,7 +6429,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10">
       <c r="A121" s="1" t="s">
         <v>257</v>
       </c>
@@ -6456,7 +6461,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10">
       <c r="A122" s="1" t="s">
         <v>262</v>
       </c>
@@ -6470,7 +6475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10">
       <c r="A123" s="1" t="s">
         <v>262</v>
       </c>
@@ -6502,7 +6507,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10">
       <c r="A124" s="1" t="s">
         <v>262</v>
       </c>
@@ -6534,7 +6539,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10">
       <c r="A125" s="1" t="s">
         <v>262</v>
       </c>
@@ -6566,7 +6571,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10">
       <c r="A126" s="1" t="s">
         <v>262</v>
       </c>
@@ -6598,7 +6603,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10">
       <c r="A127" s="1" t="s">
         <v>267</v>
       </c>
@@ -6612,7 +6617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10">
       <c r="A128" s="1" t="s">
         <v>267</v>
       </c>
@@ -6644,7 +6649,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10">
       <c r="A129" s="1" t="s">
         <v>267</v>
       </c>
@@ -6676,7 +6681,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10">
       <c r="A130" s="1" t="s">
         <v>267</v>
       </c>
@@ -6708,7 +6713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10">
       <c r="A131" s="1" t="s">
         <v>267</v>
       </c>
@@ -6740,7 +6745,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10">
       <c r="A132" s="1" t="s">
         <v>272</v>
       </c>
@@ -6754,7 +6759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10">
       <c r="A133" s="1" t="s">
         <v>272</v>
       </c>
@@ -6786,7 +6791,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10">
       <c r="A134" s="1" t="s">
         <v>272</v>
       </c>
@@ -6818,7 +6823,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10">
       <c r="A135" s="1" t="s">
         <v>272</v>
       </c>
@@ -6850,7 +6855,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10">
       <c r="A136" s="1" t="s">
         <v>272</v>
       </c>
@@ -6882,7 +6887,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10">
       <c r="A137" s="1" t="s">
         <v>277</v>
       </c>
@@ -6896,7 +6901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10">
       <c r="A138" s="1" t="s">
         <v>277</v>
       </c>
@@ -6928,7 +6933,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10">
       <c r="A139" s="1" t="s">
         <v>277</v>
       </c>
@@ -6960,7 +6965,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10">
       <c r="A140" s="1" t="s">
         <v>277</v>
       </c>
@@ -6992,7 +6997,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10">
       <c r="A141" s="1" t="s">
         <v>277</v>
       </c>
@@ -7024,7 +7029,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10">
       <c r="A142" s="1" t="s">
         <v>282</v>
       </c>
@@ -7038,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10">
       <c r="A143" s="1" t="s">
         <v>282</v>
       </c>
@@ -7070,7 +7075,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10">
       <c r="A144" s="1" t="s">
         <v>282</v>
       </c>
@@ -7102,7 +7107,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10">
       <c r="A145" s="1" t="s">
         <v>282</v>
       </c>
@@ -7134,7 +7139,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10">
       <c r="A146" s="1" t="s">
         <v>282</v>
       </c>
@@ -7166,7 +7171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10">
       <c r="A147" s="1" t="s">
         <v>287</v>
       </c>
@@ -7180,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10">
       <c r="A148" s="1" t="s">
         <v>287</v>
       </c>
@@ -7212,7 +7217,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10">
       <c r="A149" s="1" t="s">
         <v>287</v>
       </c>
@@ -7244,7 +7249,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10">
       <c r="A150" s="1" t="s">
         <v>287</v>
       </c>
@@ -7276,7 +7281,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10">
       <c r="A151" s="1" t="s">
         <v>287</v>
       </c>
@@ -7308,7 +7313,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10">
       <c r="A152" s="1" t="s">
         <v>292</v>
       </c>
@@ -7322,7 +7327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10">
       <c r="A153" s="1" t="s">
         <v>292</v>
       </c>
@@ -7354,7 +7359,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10">
       <c r="A154" s="1" t="s">
         <v>292</v>
       </c>
@@ -7386,7 +7391,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10">
       <c r="A155" s="1" t="s">
         <v>292</v>
       </c>
@@ -7418,7 +7423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10">
       <c r="A156" s="1" t="s">
         <v>292</v>
       </c>
@@ -7450,7 +7455,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10">
       <c r="A157" s="1" t="s">
         <v>297</v>
       </c>
@@ -7464,7 +7469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10">
       <c r="A158" s="1" t="s">
         <v>297</v>
       </c>
@@ -7496,7 +7501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10">
       <c r="A159" s="1" t="s">
         <v>297</v>
       </c>
@@ -7528,7 +7533,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10">
       <c r="A160" s="1" t="s">
         <v>297</v>
       </c>
@@ -7560,7 +7565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10">
       <c r="A161" s="1" t="s">
         <v>297</v>
       </c>
@@ -7592,7 +7597,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10">
       <c r="A162" s="1" t="s">
         <v>302</v>
       </c>
@@ -7606,7 +7611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10">
       <c r="A163" s="1" t="s">
         <v>302</v>
       </c>
@@ -7638,7 +7643,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10">
       <c r="A164" s="1" t="s">
         <v>302</v>
       </c>
@@ -7670,7 +7675,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10">
       <c r="A165" s="1" t="s">
         <v>302</v>
       </c>
@@ -7702,7 +7707,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10">
       <c r="A166" s="1" t="s">
         <v>302</v>
       </c>
@@ -7734,7 +7739,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10">
       <c r="A167" s="1" t="s">
         <v>307</v>
       </c>
@@ -7748,7 +7753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10">
       <c r="A168" s="1" t="s">
         <v>307</v>
       </c>
@@ -7780,7 +7785,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10">
       <c r="A169" s="1" t="s">
         <v>307</v>
       </c>
@@ -7812,7 +7817,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10">
       <c r="A170" s="1" t="s">
         <v>307</v>
       </c>
@@ -7844,7 +7849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10">
       <c r="A171" s="1" t="s">
         <v>307</v>
       </c>
@@ -7876,7 +7881,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10">
       <c r="A172" s="1" t="s">
         <v>312</v>
       </c>
@@ -7890,7 +7895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10">
       <c r="A173" s="1" t="s">
         <v>312</v>
       </c>
@@ -7922,7 +7927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10">
       <c r="A174" s="1" t="s">
         <v>315</v>
       </c>
@@ -7936,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10">
       <c r="A175" s="1" t="s">
         <v>315</v>
       </c>
@@ -7968,7 +7973,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10">
       <c r="A176" s="1" t="s">
         <v>317</v>
       </c>
@@ -7982,7 +7987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10">
       <c r="A177" s="1" t="s">
         <v>317</v>
       </c>
@@ -8014,7 +8019,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10">
       <c r="A178" s="1" t="s">
         <v>317</v>
       </c>
@@ -8046,7 +8051,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10">
       <c r="A179" s="1" t="s">
         <v>317</v>
       </c>
@@ -8078,7 +8083,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10">
       <c r="A180" s="1" t="s">
         <v>317</v>
       </c>
@@ -8110,7 +8115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10">
       <c r="A181" s="1" t="s">
         <v>317</v>
       </c>
@@ -8142,7 +8147,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10">
       <c r="A182" s="1" t="s">
         <v>317</v>
       </c>
@@ -8174,7 +8179,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10">
       <c r="A183" s="1" t="s">
         <v>317</v>
       </c>
@@ -8206,7 +8211,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10">
       <c r="A184" s="1" t="s">
         <v>317</v>
       </c>
@@ -8238,7 +8243,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10">
       <c r="A185" s="1" t="s">
         <v>317</v>
       </c>
@@ -8270,7 +8275,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10">
       <c r="A186" s="1" t="s">
         <v>317</v>
       </c>
@@ -8302,7 +8307,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10">
       <c r="A187" s="1" t="s">
         <v>329</v>
       </c>
@@ -8316,7 +8321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10">
       <c r="A188" s="1" t="s">
         <v>329</v>
       </c>
@@ -8348,7 +8353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10">
       <c r="A189" s="1" t="s">
         <v>331</v>
       </c>
@@ -8362,7 +8367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10">
       <c r="A190" s="1" t="s">
         <v>331</v>
       </c>
@@ -8394,7 +8399,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10">
       <c r="A191" s="1" t="s">
         <v>331</v>
       </c>
@@ -8426,7 +8431,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10">
       <c r="A192" s="1" t="s">
         <v>331</v>
       </c>
@@ -8458,7 +8463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10">
       <c r="A193" s="1" t="s">
         <v>331</v>
       </c>
@@ -8490,7 +8495,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10">
       <c r="A194" s="1" t="s">
         <v>336</v>
       </c>
@@ -8504,7 +8509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10">
       <c r="A195" s="1" t="s">
         <v>336</v>
       </c>
@@ -8536,7 +8541,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10">
       <c r="A196" s="1" t="s">
         <v>336</v>
       </c>
@@ -8568,7 +8573,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10">
       <c r="A197" s="1" t="s">
         <v>336</v>
       </c>
@@ -8600,7 +8605,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10">
       <c r="A198" s="1" t="s">
         <v>336</v>
       </c>
@@ -8632,7 +8637,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10">
       <c r="A199" s="1" t="s">
         <v>341</v>
       </c>
@@ -8646,7 +8651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10">
       <c r="A200" s="1" t="s">
         <v>341</v>
       </c>
@@ -8678,7 +8683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10">
       <c r="A201" s="1" t="s">
         <v>343</v>
       </c>
@@ -8692,7 +8697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10">
       <c r="A202" s="1" t="s">
         <v>343</v>
       </c>
@@ -8724,7 +8729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10">
       <c r="A203" s="1" t="s">
         <v>345</v>
       </c>
@@ -8738,7 +8743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10">
       <c r="A204" s="1" t="s">
         <v>345</v>
       </c>
@@ -8770,7 +8775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10">
       <c r="A205" s="1" t="s">
         <v>347</v>
       </c>
@@ -8784,7 +8789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10">
       <c r="A206" s="1" t="s">
         <v>347</v>
       </c>
@@ -8816,7 +8821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10">
       <c r="A207" s="1" t="s">
         <v>349</v>
       </c>
@@ -8830,7 +8835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10">
       <c r="A208" s="1" t="s">
         <v>349</v>
       </c>
@@ -8862,7 +8867,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10">
       <c r="A209" s="1" t="s">
         <v>349</v>
       </c>
@@ -8894,7 +8899,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10">
       <c r="A210" s="1" t="s">
         <v>349</v>
       </c>
@@ -8926,7 +8931,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10">
       <c r="A211" s="1" t="s">
         <v>349</v>
       </c>
@@ -8958,7 +8963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10">
       <c r="A212" s="1" t="s">
         <v>354</v>
       </c>
@@ -8972,7 +8977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10">
       <c r="A213" s="1" t="s">
         <v>354</v>
       </c>
@@ -9004,7 +9009,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10">
       <c r="A214" s="1" t="s">
         <v>354</v>
       </c>
@@ -9036,7 +9041,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10">
       <c r="A215" s="1" t="s">
         <v>354</v>
       </c>
@@ -9068,7 +9073,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10">
       <c r="A216" s="1" t="s">
         <v>354</v>
       </c>
@@ -9100,7 +9105,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10">
       <c r="A217" s="1" t="s">
         <v>359</v>
       </c>
@@ -9114,7 +9119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10">
       <c r="A218" s="1" t="s">
         <v>359</v>
       </c>
@@ -9146,7 +9151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10">
       <c r="A219" s="1" t="s">
         <v>359</v>
       </c>
@@ -9178,7 +9183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10">
       <c r="A220" s="1" t="s">
         <v>359</v>
       </c>
@@ -9210,7 +9215,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10">
       <c r="A221" s="1" t="s">
         <v>359</v>
       </c>
@@ -9242,7 +9247,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10">
       <c r="A222" s="1" t="s">
         <v>364</v>
       </c>
@@ -9256,7 +9261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10">
       <c r="A223" s="1" t="s">
         <v>364</v>
       </c>
@@ -9288,7 +9293,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10">
       <c r="A224" s="1" t="s">
         <v>364</v>
       </c>
@@ -9320,7 +9325,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10">
       <c r="A225" s="1" t="s">
         <v>364</v>
       </c>
@@ -9352,7 +9357,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10">
       <c r="A226" s="1" t="s">
         <v>364</v>
       </c>
@@ -9384,7 +9389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10">
       <c r="A227" s="1" t="s">
         <v>369</v>
       </c>
@@ -9398,7 +9403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10">
       <c r="A228" s="1" t="s">
         <v>369</v>
       </c>
@@ -9430,7 +9435,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10">
       <c r="A229" s="1" t="s">
         <v>369</v>
       </c>
@@ -9462,7 +9467,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10">
       <c r="A230" s="1" t="s">
         <v>369</v>
       </c>
@@ -9494,7 +9499,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10">
       <c r="A231" s="1" t="s">
         <v>369</v>
       </c>
@@ -9526,7 +9531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10">
       <c r="A232" s="1" t="s">
         <v>374</v>
       </c>
@@ -9540,7 +9545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10">
       <c r="A233" s="1" t="s">
         <v>374</v>
       </c>
@@ -9572,7 +9577,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10">
       <c r="A234" s="1" t="s">
         <v>374</v>
       </c>
@@ -9604,7 +9609,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10">
       <c r="A235" s="1" t="s">
         <v>374</v>
       </c>
@@ -9636,7 +9641,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10">
       <c r="A236" s="1" t="s">
         <v>374</v>
       </c>
@@ -9668,7 +9673,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10">
       <c r="A237" s="1" t="s">
         <v>379</v>
       </c>
@@ -9682,7 +9687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10">
       <c r="A238" s="1" t="s">
         <v>379</v>
       </c>
@@ -9714,7 +9719,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10">
       <c r="A239" s="1" t="s">
         <v>381</v>
       </c>
@@ -9728,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10">
       <c r="A240" s="1" t="s">
         <v>381</v>
       </c>
@@ -9760,7 +9765,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10">
       <c r="A241" s="1" t="s">
         <v>383</v>
       </c>
@@ -9774,7 +9779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10">
       <c r="A242" s="1" t="s">
         <v>383</v>
       </c>
@@ -9806,7 +9811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10">
       <c r="A243" s="1" t="s">
         <v>386</v>
       </c>
@@ -9820,7 +9825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10">
       <c r="A244" s="1" t="s">
         <v>386</v>
       </c>
@@ -9852,7 +9857,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10">
       <c r="A245" s="1" t="s">
         <v>389</v>
       </c>
@@ -9866,7 +9871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10">
       <c r="A246" s="1" t="s">
         <v>389</v>
       </c>
@@ -9898,7 +9903,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10">
       <c r="A247" s="1" t="s">
         <v>389</v>
       </c>
@@ -9930,7 +9935,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10">
       <c r="A248" s="1" t="s">
         <v>389</v>
       </c>
@@ -9962,7 +9967,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10">
       <c r="A249" s="1" t="s">
         <v>389</v>
       </c>
@@ -9994,7 +9999,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10">
       <c r="A250" s="1" t="s">
         <v>389</v>
       </c>
@@ -10026,7 +10031,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10">
       <c r="A251" s="1" t="s">
         <v>389</v>
       </c>
@@ -10058,7 +10063,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10">
       <c r="A252" s="1" t="s">
         <v>389</v>
       </c>
@@ -10090,7 +10095,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10">
       <c r="A253" s="1" t="s">
         <v>389</v>
       </c>
@@ -10122,7 +10127,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10">
       <c r="A254" s="1" t="s">
         <v>389</v>
       </c>
@@ -10154,7 +10159,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10">
       <c r="A255" s="1" t="s">
         <v>389</v>
       </c>
@@ -10186,7 +10191,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10">
       <c r="A256" s="1" t="s">
         <v>389</v>
       </c>
@@ -10218,7 +10223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10">
       <c r="A257" s="1" t="s">
         <v>389</v>
       </c>
@@ -10250,7 +10255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10">
       <c r="A258" s="1" t="s">
         <v>389</v>
       </c>
@@ -10282,7 +10287,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10">
       <c r="A259" s="1" t="s">
         <v>389</v>
       </c>
@@ -10314,7 +10319,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10">
       <c r="A260" s="1" t="s">
         <v>389</v>
       </c>
@@ -10346,7 +10351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10">
       <c r="A261" s="1" t="s">
         <v>389</v>
       </c>
@@ -10378,7 +10383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10">
       <c r="A262" s="1" t="s">
         <v>389</v>
       </c>
@@ -10410,7 +10415,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10">
       <c r="A263" s="1" t="s">
         <v>389</v>
       </c>
@@ -10442,7 +10447,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10">
       <c r="A264" s="1" t="s">
         <v>389</v>
       </c>
@@ -10474,7 +10479,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10">
       <c r="A265" s="1" t="s">
         <v>389</v>
       </c>
@@ -10506,7 +10511,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10">
       <c r="A266" s="1" t="s">
         <v>410</v>
       </c>
@@ -10520,7 +10525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10">
       <c r="A267" s="1" t="s">
         <v>410</v>
       </c>
@@ -10552,7 +10557,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10">
       <c r="A268" s="1" t="s">
         <v>410</v>
       </c>
@@ -10584,7 +10589,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10">
       <c r="A269" s="1" t="s">
         <v>410</v>
       </c>
@@ -10616,7 +10621,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10">
       <c r="A270" s="1" t="s">
         <v>410</v>
       </c>
@@ -10648,7 +10653,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10">
       <c r="A271" s="1" t="s">
         <v>410</v>
       </c>
@@ -10680,7 +10685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10">
       <c r="A272" s="1" t="s">
         <v>410</v>
       </c>
@@ -10712,7 +10717,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10">
       <c r="A273" s="1" t="s">
         <v>410</v>
       </c>
@@ -10744,7 +10749,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10">
       <c r="A274" s="1" t="s">
         <v>410</v>
       </c>
@@ -10776,7 +10781,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10">
       <c r="A275" s="1" t="s">
         <v>410</v>
       </c>
@@ -10808,7 +10813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10">
       <c r="A276" s="1" t="s">
         <v>410</v>
       </c>
@@ -10840,7 +10845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10">
       <c r="A277" s="1" t="s">
         <v>410</v>
       </c>
@@ -10872,7 +10877,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10">
       <c r="A278" s="1" t="s">
         <v>410</v>
       </c>
@@ -10904,7 +10909,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10">
       <c r="A279" s="1" t="s">
         <v>410</v>
       </c>
@@ -10936,7 +10941,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10">
       <c r="A280" s="1" t="s">
         <v>410</v>
       </c>
@@ -10968,7 +10973,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10">
       <c r="A281" s="1" t="s">
         <v>410</v>
       </c>
@@ -11000,7 +11005,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10">
       <c r="A282" s="1" t="s">
         <v>410</v>
       </c>
@@ -11032,7 +11037,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10">
       <c r="A283" s="1" t="s">
         <v>410</v>
       </c>
@@ -11064,7 +11069,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10">
       <c r="A284" s="1" t="s">
         <v>410</v>
       </c>
@@ -11096,7 +11101,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10">
       <c r="A285" s="1" t="s">
         <v>410</v>
       </c>
@@ -11128,7 +11133,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10">
       <c r="A286" s="1" t="s">
         <v>410</v>
       </c>
@@ -11160,7 +11165,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10">
       <c r="A287" s="1" t="s">
         <v>431</v>
       </c>
@@ -11174,7 +11179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10">
       <c r="A288" s="1" t="s">
         <v>431</v>
       </c>
@@ -11206,7 +11211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10">
       <c r="A289" s="1" t="s">
         <v>431</v>
       </c>
@@ -11238,7 +11243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10">
       <c r="A290" s="1" t="s">
         <v>431</v>
       </c>
@@ -11270,7 +11275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10">
       <c r="A291" s="1" t="s">
         <v>431</v>
       </c>
@@ -11302,7 +11307,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10">
       <c r="A292" s="1" t="s">
         <v>437</v>
       </c>
@@ -11316,7 +11321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10">
       <c r="A293" s="1" t="s">
         <v>437</v>
       </c>
@@ -11348,7 +11353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10">
       <c r="A294" s="1" t="s">
         <v>437</v>
       </c>
@@ -11380,7 +11385,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10">
       <c r="A295" s="1" t="s">
         <v>437</v>
       </c>
@@ -11412,7 +11417,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10">
       <c r="A296" s="1" t="s">
         <v>437</v>
       </c>
@@ -11444,7 +11449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10">
       <c r="A297" s="1" t="s">
         <v>443</v>
       </c>
@@ -11458,7 +11463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10">
       <c r="A298" s="1" t="s">
         <v>443</v>
       </c>
@@ -11490,7 +11495,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10">
       <c r="A299" s="1" t="s">
         <v>443</v>
       </c>
@@ -11522,7 +11527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10">
       <c r="A300" s="1" t="s">
         <v>443</v>
       </c>
@@ -11554,7 +11559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10">
       <c r="A301" s="1" t="s">
         <v>443</v>
       </c>
@@ -11586,7 +11591,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10">
       <c r="A302" s="1" t="s">
         <v>448</v>
       </c>
@@ -11600,7 +11605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10">
       <c r="A303" s="1" t="s">
         <v>448</v>
       </c>
@@ -11632,7 +11637,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10">
       <c r="A304" s="1" t="s">
         <v>448</v>
       </c>
@@ -11664,7 +11669,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10">
       <c r="A305" s="1" t="s">
         <v>448</v>
       </c>
@@ -11696,7 +11701,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10">
       <c r="A306" s="1" t="s">
         <v>448</v>
       </c>
@@ -11728,7 +11733,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10">
       <c r="A307" s="1" t="s">
         <v>448</v>
       </c>
@@ -11760,7 +11765,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10">
       <c r="A308" s="1" t="s">
         <v>448</v>
       </c>
@@ -11792,7 +11797,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10">
       <c r="A309" s="1" t="s">
         <v>448</v>
       </c>
@@ -11824,7 +11829,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10">
       <c r="A310" s="1" t="s">
         <v>448</v>
       </c>
@@ -11856,7 +11861,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10">
       <c r="A311" s="1" t="s">
         <v>448</v>
       </c>
@@ -11896,12 +11901,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H137"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -11927,7 +11932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -11953,7 +11958,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>100</v>
       </c>
@@ -11979,7 +11984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>103</v>
       </c>
@@ -12005,7 +12010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>106</v>
       </c>
@@ -12031,7 +12036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -12057,7 +12062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
@@ -12083,7 +12088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>115</v>
       </c>
@@ -12109,7 +12114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>117</v>
       </c>
@@ -12135,7 +12140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>117</v>
       </c>
@@ -12161,7 +12166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>117</v>
       </c>
@@ -12187,7 +12192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>122</v>
       </c>
@@ -12213,7 +12218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>122</v>
       </c>
@@ -12239,7 +12244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>122</v>
       </c>
@@ -12265,7 +12270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>122</v>
       </c>
@@ -12291,7 +12296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>128</v>
       </c>
@@ -12317,7 +12322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>128</v>
       </c>
@@ -12343,7 +12348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>128</v>
       </c>
@@ -12369,7 +12374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>132</v>
       </c>
@@ -12395,7 +12400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>132</v>
       </c>
@@ -12421,7 +12426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>132</v>
       </c>
@@ -12447,7 +12452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>132</v>
       </c>
@@ -12473,7 +12478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>135</v>
       </c>
@@ -12499,7 +12504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>135</v>
       </c>
@@ -12525,7 +12530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
         <v>135</v>
       </c>
@@ -12551,7 +12556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>135</v>
       </c>
@@ -12577,7 +12582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
         <v>141</v>
       </c>
@@ -12603,7 +12608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
         <v>141</v>
       </c>
@@ -12629,7 +12634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>141</v>
       </c>
@@ -12655,7 +12660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -12681,7 +12686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
         <v>141</v>
       </c>
@@ -12707,7 +12712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
         <v>148</v>
       </c>
@@ -12733,7 +12738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>148</v>
       </c>
@@ -12759,7 +12764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
         <v>148</v>
       </c>
@@ -12785,7 +12790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>148</v>
       </c>
@@ -12811,7 +12816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
         <v>154</v>
       </c>
@@ -12837,7 +12842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
         <v>154</v>
       </c>
@@ -12863,7 +12868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
         <v>154</v>
       </c>
@@ -12889,7 +12894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
         <v>154</v>
       </c>
@@ -12915,7 +12920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
         <v>154</v>
       </c>
@@ -12941,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
         <v>162</v>
       </c>
@@ -12967,7 +12972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
         <v>162</v>
       </c>
@@ -12993,7 +12998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
         <v>162</v>
       </c>
@@ -13019,7 +13024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
         <v>162</v>
       </c>
@@ -13045,7 +13050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
         <v>170</v>
       </c>
@@ -13071,7 +13076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
         <v>170</v>
       </c>
@@ -13097,7 +13102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
         <v>170</v>
       </c>
@@ -13123,7 +13128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
         <v>170</v>
       </c>
@@ -13149,7 +13154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
         <v>177</v>
       </c>
@@ -13175,7 +13180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
         <v>177</v>
       </c>
@@ -13201,7 +13206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
         <v>177</v>
       </c>
@@ -13227,7 +13232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
         <v>177</v>
       </c>
@@ -13253,7 +13258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
         <v>177</v>
       </c>
@@ -13279,7 +13284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
         <v>188</v>
       </c>
@@ -13305,7 +13310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
         <v>193</v>
       </c>
@@ -13331,7 +13336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
         <v>193</v>
       </c>
@@ -13357,7 +13362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
         <v>193</v>
       </c>
@@ -13383,7 +13388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
         <v>193</v>
       </c>
@@ -13409,7 +13414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
         <v>193</v>
       </c>
@@ -13435,7 +13440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
         <v>202</v>
       </c>
@@ -13461,7 +13466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
         <v>202</v>
       </c>
@@ -13487,7 +13492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
         <v>202</v>
       </c>
@@ -13513,7 +13518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
         <v>202</v>
       </c>
@@ -13539,7 +13544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
         <v>208</v>
       </c>
@@ -13565,7 +13570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
         <v>214</v>
       </c>
@@ -13591,7 +13596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
         <v>220</v>
       </c>
@@ -13617,7 +13622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
         <v>225</v>
       </c>
@@ -13643,7 +13648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
         <v>230</v>
       </c>
@@ -13669,7 +13674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
         <v>235</v>
       </c>
@@ -13695,7 +13700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
         <v>235</v>
       </c>
@@ -13721,7 +13726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
         <v>235</v>
       </c>
@@ -13747,7 +13752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
         <v>243</v>
       </c>
@@ -13773,7 +13778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
         <v>249</v>
       </c>
@@ -13799,7 +13804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
         <v>251</v>
       </c>
@@ -13825,7 +13830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
         <v>257</v>
       </c>
@@ -13851,7 +13856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
         <v>262</v>
       </c>
@@ -13877,7 +13882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
         <v>267</v>
       </c>
@@ -13903,7 +13908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
         <v>272</v>
       </c>
@@ -13929,7 +13934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
         <v>277</v>
       </c>
@@ -13955,7 +13960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
         <v>277</v>
       </c>
@@ -13981,7 +13986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
         <v>277</v>
       </c>
@@ -14007,7 +14012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
         <v>277</v>
       </c>
@@ -14033,7 +14038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
         <v>282</v>
       </c>
@@ -14059,7 +14064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
         <v>282</v>
       </c>
@@ -14085,7 +14090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
         <v>282</v>
       </c>
@@ -14111,7 +14116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
         <v>282</v>
       </c>
@@ -14137,7 +14142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
         <v>282</v>
       </c>
@@ -14163,7 +14168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
         <v>287</v>
       </c>
@@ -14189,7 +14194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
         <v>287</v>
       </c>
@@ -14215,7 +14220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
         <v>287</v>
       </c>
@@ -14241,7 +14246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
         <v>292</v>
       </c>
@@ -14267,7 +14272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
         <v>292</v>
       </c>
@@ -14293,7 +14298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
         <v>292</v>
       </c>
@@ -14319,7 +14324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
         <v>297</v>
       </c>
@@ -14345,7 +14350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
         <v>297</v>
       </c>
@@ -14371,7 +14376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
         <v>297</v>
       </c>
@@ -14397,7 +14402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
         <v>302</v>
       </c>
@@ -14423,7 +14428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
         <v>302</v>
       </c>
@@ -14449,7 +14454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
         <v>302</v>
       </c>
@@ -14475,7 +14480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
         <v>307</v>
       </c>
@@ -14501,7 +14506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
         <v>307</v>
       </c>
@@ -14527,7 +14532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
         <v>307</v>
       </c>
@@ -14553,7 +14558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
         <v>312</v>
       </c>
@@ -14579,7 +14584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
         <v>315</v>
       </c>
@@ -14605,7 +14610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
         <v>317</v>
       </c>
@@ -14631,7 +14636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
         <v>329</v>
       </c>
@@ -14657,7 +14662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
         <v>331</v>
       </c>
@@ -14683,7 +14688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
         <v>331</v>
       </c>
@@ -14709,7 +14714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
         <v>336</v>
       </c>
@@ -14735,7 +14740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
         <v>341</v>
       </c>
@@ -14761,7 +14766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
         <v>343</v>
       </c>
@@ -14787,7 +14792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
         <v>345</v>
       </c>
@@ -14813,7 +14818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
         <v>347</v>
       </c>
@@ -14839,7 +14844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
         <v>349</v>
       </c>
@@ -14865,7 +14870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
         <v>354</v>
       </c>
@@ -14891,7 +14896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
         <v>359</v>
       </c>
@@ -14917,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
         <v>364</v>
       </c>
@@ -14943,7 +14948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
         <v>369</v>
       </c>
@@ -14969,7 +14974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
         <v>374</v>
       </c>
@@ -14995,7 +15000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
         <v>379</v>
       </c>
@@ -15021,7 +15026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
         <v>381</v>
       </c>
@@ -15047,7 +15052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
         <v>383</v>
       </c>
@@ -15073,7 +15078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
         <v>386</v>
       </c>
@@ -15099,7 +15104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
         <v>389</v>
       </c>
@@ -15125,7 +15130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
         <v>389</v>
       </c>
@@ -15151,7 +15156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
         <v>389</v>
       </c>
@@ -15177,7 +15182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
         <v>389</v>
       </c>
@@ -15203,7 +15208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
         <v>389</v>
       </c>
@@ -15229,7 +15234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
         <v>410</v>
       </c>
@@ -15255,7 +15260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8">
       <c r="A130" s="1" t="s">
         <v>410</v>
       </c>
@@ -15281,7 +15286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
         <v>410</v>
       </c>
@@ -15307,7 +15312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
         <v>410</v>
       </c>
@@ -15333,7 +15338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
         <v>410</v>
       </c>
@@ -15359,7 +15364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" s="1" t="s">
         <v>431</v>
       </c>
@@ -15385,7 +15390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
         <v>437</v>
       </c>
@@ -15411,7 +15416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" s="1" t="s">
         <v>443</v>
       </c>
@@ -15437,7 +15442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
         <v>448</v>
       </c>
@@ -15471,9 +15476,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -15499,7 +15504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -15525,7 +15530,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>100</v>
       </c>
@@ -15551,7 +15556,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>103</v>
       </c>
@@ -15577,7 +15582,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>106</v>
       </c>
@@ -15603,7 +15608,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -15629,7 +15634,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
@@ -15655,7 +15660,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>115</v>
       </c>
@@ -15681,7 +15686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>117</v>
       </c>
@@ -15707,7 +15712,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>122</v>
       </c>
@@ -15733,7 +15738,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>128</v>
       </c>
@@ -15759,7 +15764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>132</v>
       </c>
@@ -15785,7 +15790,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>135</v>
       </c>
@@ -15811,7 +15816,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>141</v>
       </c>
@@ -15837,7 +15842,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>148</v>
       </c>
@@ -15863,7 +15868,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>154</v>
       </c>
@@ -15889,7 +15894,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>162</v>
       </c>
@@ -15915,7 +15920,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>170</v>
       </c>
@@ -15941,7 +15946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>177</v>
       </c>
@@ -15967,7 +15972,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>188</v>
       </c>
@@ -15993,7 +15998,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>193</v>
       </c>
@@ -16019,7 +16024,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>202</v>
       </c>
@@ -16045,7 +16050,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
         <v>208</v>
       </c>
@@ -16071,7 +16076,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
         <v>214</v>
       </c>
@@ -16097,7 +16102,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
         <v>220</v>
       </c>
@@ -16123,7 +16128,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
         <v>225</v>
       </c>
@@ -16149,7 +16154,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
         <v>230</v>
       </c>
@@ -16175,7 +16180,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
         <v>235</v>
       </c>
@@ -16201,7 +16206,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
         <v>243</v>
       </c>
@@ -16227,7 +16232,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
         <v>249</v>
       </c>
@@ -16253,7 +16258,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
         <v>459</v>
       </c>
@@ -16279,7 +16284,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
         <v>460</v>
       </c>
@@ -16305,7 +16310,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>461</v>
       </c>
@@ -16331,7 +16336,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
         <v>462</v>
       </c>
@@ -16357,7 +16362,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>463</v>
       </c>
@@ -16383,7 +16388,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
         <v>251</v>
       </c>
@@ -16409,7 +16414,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
         <v>257</v>
       </c>
@@ -16435,7 +16440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
         <v>262</v>
       </c>
@@ -16461,7 +16466,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
         <v>267</v>
       </c>
@@ -16487,7 +16492,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
         <v>272</v>
       </c>
@@ -16513,7 +16518,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
         <v>277</v>
       </c>
@@ -16539,7 +16544,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
         <v>282</v>
       </c>
@@ -16565,7 +16570,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
         <v>287</v>
       </c>
@@ -16591,7 +16596,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
         <v>292</v>
       </c>
@@ -16617,7 +16622,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
         <v>297</v>
       </c>
@@ -16643,7 +16648,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
         <v>302</v>
       </c>
@@ -16669,7 +16674,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
         <v>307</v>
       </c>
@@ -16695,7 +16700,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
         <v>312</v>
       </c>
@@ -16721,7 +16726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
         <v>315</v>
       </c>
@@ -16747,7 +16752,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
         <v>317</v>
       </c>
@@ -16773,7 +16778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
         <v>329</v>
       </c>
@@ -16799,7 +16804,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
         <v>331</v>
       </c>
@@ -16825,7 +16830,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
         <v>336</v>
       </c>
@@ -16851,7 +16856,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
         <v>341</v>
       </c>
@@ -16877,7 +16882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
         <v>343</v>
       </c>
@@ -16903,7 +16908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
         <v>345</v>
       </c>
@@ -16929,7 +16934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
         <v>347</v>
       </c>
@@ -16955,7 +16960,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
         <v>349</v>
       </c>
@@ -16981,7 +16986,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
         <v>354</v>
       </c>
@@ -17007,7 +17012,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
         <v>359</v>
       </c>
@@ -17033,7 +17038,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
         <v>364</v>
       </c>
@@ -17059,7 +17064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
         <v>369</v>
       </c>
@@ -17085,7 +17090,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
         <v>374</v>
       </c>
@@ -17111,7 +17116,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
         <v>379</v>
       </c>
@@ -17137,7 +17142,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
         <v>381</v>
       </c>
@@ -17163,7 +17168,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
         <v>383</v>
       </c>
@@ -17189,7 +17194,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
         <v>386</v>
       </c>
@@ -17215,7 +17220,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
         <v>389</v>
       </c>
@@ -17241,7 +17246,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
         <v>410</v>
       </c>
@@ -17267,7 +17272,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
         <v>464</v>
       </c>
@@ -17293,7 +17298,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
         <v>465</v>
       </c>
@@ -17319,7 +17324,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
         <v>431</v>
       </c>
@@ -17345,7 +17350,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
         <v>466</v>
       </c>
@@ -17371,7 +17376,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
         <v>467</v>
       </c>
@@ -17397,7 +17402,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
         <v>437</v>
       </c>
@@ -17423,7 +17428,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
         <v>443</v>
       </c>
@@ -17449,7 +17454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
         <v>448</v>
       </c>
@@ -17475,7 +17480,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
         <v>468</v>
       </c>
@@ -17501,7 +17506,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
         <v>469</v>
       </c>
@@ -17527,7 +17532,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
         <v>470</v>
       </c>
@@ -17553,7 +17558,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
         <v>471</v>
       </c>
@@ -17579,7 +17584,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
         <v>472</v>
       </c>
@@ -17605,7 +17610,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
         <v>473</v>
       </c>
@@ -17631,111 +17636,111 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+    <row r="84" spans="1:8">
+      <c r="A84" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B84" s="1">
-        <v>0</v>
-      </c>
-      <c r="C84" s="1">
-        <v>-5573</v>
-      </c>
-      <c r="D84" s="1">
-        <v>507</v>
-      </c>
-      <c r="E84" s="1">
-        <v>-3043</v>
-      </c>
-      <c r="F84" s="1">
+      <c r="B84" s="2">
+        <v>0</v>
+      </c>
+      <c r="C84" s="2">
+        <v>-5290</v>
+      </c>
+      <c r="D84" s="2">
+        <v>429</v>
+      </c>
+      <c r="E84" s="2">
+        <v>-3063</v>
+      </c>
+      <c r="F84" s="2">
         <v>80</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G84" s="2">
         <v>200</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H84" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+    <row r="85" spans="1:8">
+      <c r="A85" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B85" s="1">
-        <v>0</v>
-      </c>
-      <c r="C85" s="1">
-        <v>-5573</v>
-      </c>
-      <c r="D85" s="1">
-        <v>518</v>
-      </c>
-      <c r="E85" s="1">
-        <v>-3052</v>
-      </c>
-      <c r="F85" s="1">
+      <c r="B85" s="2">
+        <v>0</v>
+      </c>
+      <c r="C85" s="2">
+        <v>-5290</v>
+      </c>
+      <c r="D85" s="2">
+        <v>429</v>
+      </c>
+      <c r="E85" s="2">
+        <v>-3063</v>
+      </c>
+      <c r="F85" s="2">
         <v>80</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G85" s="2">
         <v>200</v>
       </c>
-      <c r="H85" s="1">
+      <c r="H85" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+    <row r="86" spans="1:8">
+      <c r="A86" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B86" s="1">
-        <v>0</v>
-      </c>
-      <c r="C86" s="1">
-        <v>-5371</v>
-      </c>
-      <c r="D86" s="1">
-        <v>503</v>
-      </c>
-      <c r="E86" s="1">
-        <v>-3045</v>
-      </c>
-      <c r="F86" s="1">
+      <c r="B86" s="2">
+        <v>0</v>
+      </c>
+      <c r="C86" s="2">
+        <v>-5176</v>
+      </c>
+      <c r="D86" s="2">
+        <v>429</v>
+      </c>
+      <c r="E86" s="2">
+        <v>-3063</v>
+      </c>
+      <c r="F86" s="2">
         <v>80</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G86" s="2">
         <v>200</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H86" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+    <row r="87" spans="1:8">
+      <c r="A87" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B87" s="1">
-        <v>0</v>
-      </c>
-      <c r="C87" s="1">
-        <v>-5369</v>
-      </c>
-      <c r="D87" s="1">
-        <v>515</v>
-      </c>
-      <c r="E87" s="1">
-        <v>-3050</v>
-      </c>
-      <c r="F87" s="1">
+      <c r="B87" s="2">
+        <v>0</v>
+      </c>
+      <c r="C87" s="2">
+        <v>-5176</v>
+      </c>
+      <c r="D87" s="2">
+        <v>429</v>
+      </c>
+      <c r="E87" s="2">
+        <v>-3063</v>
+      </c>
+      <c r="F87" s="2">
         <v>80</v>
       </c>
-      <c r="G87" s="1">
+      <c r="G87" s="2">
         <v>200</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H87" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
         <v>478</v>
       </c>
@@ -17743,13 +17748,13 @@
         <v>0</v>
       </c>
       <c r="C88" s="1">
-        <v>-5473</v>
+        <v>-5234</v>
       </c>
       <c r="D88" s="1">
-        <v>517</v>
+        <v>429</v>
       </c>
       <c r="E88" s="1">
-        <v>-3049</v>
+        <v>-3063</v>
       </c>
       <c r="F88" s="1">
         <v>80</v>
@@ -17761,7 +17766,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
         <v>479</v>
       </c>
@@ -17769,13 +17774,13 @@
         <v>0</v>
       </c>
       <c r="C89" s="1">
-        <v>-5478</v>
+        <v>-5234</v>
       </c>
       <c r="D89" s="1">
-        <v>507</v>
+        <v>429</v>
       </c>
       <c r="E89" s="1">
-        <v>-3043</v>
+        <v>-3063</v>
       </c>
       <c r="F89" s="1">
         <v>80</v>
@@ -17787,7 +17792,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
         <v>480</v>
       </c>
@@ -17813,7 +17818,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
         <v>481</v>
       </c>
@@ -17839,7 +17844,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
         <v>482</v>
       </c>
@@ -17865,7 +17870,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
         <v>483</v>
       </c>
@@ -17899,9 +17904,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>484</v>
       </c>
@@ -17924,7 +17929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>485</v>
       </c>
@@ -17947,7 +17952,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -17970,7 +17975,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>61</v>
       </c>
@@ -17993,7 +17998,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>121</v>
       </c>
@@ -18016,7 +18021,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>181</v>
       </c>
@@ -18039,7 +18044,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>241</v>
       </c>
@@ -18062,7 +18067,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -18085,7 +18090,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>61</v>
       </c>
@@ -18108,7 +18113,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>121</v>
       </c>
@@ -18131,7 +18136,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>181</v>
       </c>
@@ -18154,7 +18159,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>241</v>
       </c>
@@ -18177,7 +18182,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -18200,7 +18205,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>61</v>
       </c>
@@ -18223,7 +18228,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>121</v>
       </c>
@@ -18246,7 +18251,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>181</v>
       </c>
@@ -18269,7 +18274,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>241</v>
       </c>
@@ -18292,7 +18297,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -18315,7 +18320,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>61</v>
       </c>
@@ -18338,7 +18343,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>121</v>
       </c>
